--- a/test-case-exports/PaymentLinks.xlsx
+++ b/test-case-exports/PaymentLinks.xlsx
@@ -332,7 +332,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-08T15:08:53.493Z</t>
+    <t>2026-09-09T06:44:10.129Z</t>
   </si>
   <si>
     <t>Total test cases</t>
